--- a/Zinc/4. Exploratory data analysis/Normality_checks.xlsx
+++ b/Zinc/4. Exploratory data analysis/Normality_checks.xlsx
@@ -948,7 +948,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>2.49729594453213</v>
+        <v>2.39780468214961</v>
       </c>
     </row>
     <row r="19">
@@ -959,7 +959,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>6.188471916066</v>
+        <v>6.54960935065161</v>
       </c>
     </row>
     <row r="20">
@@ -970,7 +970,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>9.22841682466233</v>
+        <v>9.25979686301714</v>
       </c>
     </row>
     <row r="21">
@@ -981,7 +981,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>6.43827227328214</v>
+        <v>6.78410818134828</v>
       </c>
     </row>
     <row r="22">
@@ -992,7 +992,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>2.1996824357861</v>
+        <v>2.16944583764421</v>
       </c>
     </row>
     <row r="23">
@@ -1003,7 +1003,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>2.51233871275674</v>
+        <v>2.49552581992415</v>
       </c>
     </row>
     <row r="24">
@@ -1014,7 +1014,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>4.4358300437397</v>
+        <v>4.43710556758998</v>
       </c>
     </row>
     <row r="25">
@@ -1025,7 +1025,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>-10.1871446959221</v>
+        <v>-10.5821690339725</v>
       </c>
     </row>
     <row r="26">
@@ -1036,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>2.23383168486604</v>
+        <v>1.98134305749219</v>
       </c>
     </row>
     <row r="27">
@@ -1047,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>5.18284830037465</v>
+        <v>4.19313242939553</v>
       </c>
     </row>
     <row r="28">
@@ -1058,7 +1058,7 @@
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>-2.82360964163951</v>
+        <v>-2.82431441042732</v>
       </c>
     </row>
     <row r="29">
@@ -1069,7 +1069,7 @@
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>10.8005922632227</v>
+        <v>10.7980521095364</v>
       </c>
     </row>
     <row r="30">
@@ -1080,7 +1080,7 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.202544678355585</v>
+        <v>0.205362209623964</v>
       </c>
     </row>
     <row r="31">
@@ -1091,7 +1091,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>1.84471536408702</v>
+        <v>1.84770316050052</v>
       </c>
     </row>
     <row r="32">
@@ -1102,7 +1102,7 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>6.17281251617355</v>
+        <v>6.74392287889955</v>
       </c>
     </row>
     <row r="33">
@@ -1113,7 +1113,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.664546207661826</v>
+        <v>-0.664357950331671</v>
       </c>
     </row>
     <row r="34">
@@ -1124,7 +1124,7 @@
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>2.47411042756224</v>
+        <v>2.47456549912939</v>
       </c>
     </row>
     <row r="35">
@@ -1135,7 +1135,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>16.4218761825449</v>
+        <v>16.6088988410897</v>
       </c>
     </row>
     <row r="36">
@@ -1146,7 +1146,7 @@
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>12.5888727271131</v>
+        <v>11.5798282809064</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>0.252829596764858</v>
+        <v>0.251630755758867</v>
       </c>
     </row>
     <row r="38">
@@ -1168,7 +1168,7 @@
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>7.37478377102132</v>
+        <v>7.37529819940036</v>
       </c>
     </row>
     <row r="39">
@@ -1179,7 +1179,7 @@
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>1.77298331310007</v>
+        <v>1.77235748803335</v>
       </c>
     </row>
     <row r="40">
@@ -1190,7 +1190,7 @@
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>0.174548980742531</v>
+        <v>0.174727936891033</v>
       </c>
     </row>
     <row r="41">
@@ -1201,7 +1201,7 @@
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>7.2070761259635</v>
+        <v>7.20684904538553</v>
       </c>
     </row>
     <row r="42">
@@ -1212,7 +1212,7 @@
         <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>1.004676147866</v>
+        <v>1.00450045881068</v>
       </c>
     </row>
     <row r="43">
@@ -1223,7 +1223,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>4.28909721799728</v>
+        <v>4.14132329461224</v>
       </c>
     </row>
     <row r="44">
@@ -1234,7 +1234,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="n">
-        <v>3.2584891927878</v>
+        <v>3.3171135614733</v>
       </c>
     </row>
     <row r="45">
@@ -1245,7 +1245,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>3.46625703766325</v>
+        <v>3.62270224266998</v>
       </c>
     </row>
     <row r="46">
@@ -1256,7 +1256,7 @@
         <v>4</v>
       </c>
       <c r="C46" t="n">
-        <v>13.6543329574097</v>
+        <v>13.8116015538048</v>
       </c>
     </row>
     <row r="47">
@@ -1267,7 +1267,7 @@
         <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>16.4207020886032</v>
+        <v>16.6564858232989</v>
       </c>
     </row>
     <row r="48">
@@ -1278,7 +1278,7 @@
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>0.32054073838517</v>
+        <v>0.46368978881607</v>
       </c>
     </row>
     <row r="49">
@@ -1509,7 +1509,7 @@
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>2.49729594453213</v>
+        <v>2.39780468214961</v>
       </c>
     </row>
     <row r="70">
@@ -1520,7 +1520,7 @@
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>2.49729594453213</v>
+        <v>2.3978046821496</v>
       </c>
     </row>
     <row r="71">
@@ -1531,7 +1531,7 @@
         <v>4</v>
       </c>
       <c r="C71" t="n">
-        <v>6.188471916066</v>
+        <v>6.54960935065161</v>
       </c>
     </row>
     <row r="72">
@@ -1542,7 +1542,7 @@
         <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>6.188471916066</v>
+        <v>6.5496093506516</v>
       </c>
     </row>
     <row r="73">
@@ -1553,7 +1553,7 @@
         <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>9.22841682466233</v>
+        <v>9.25979686301714</v>
       </c>
     </row>
     <row r="74">
@@ -1564,7 +1564,7 @@
         <v>4</v>
       </c>
       <c r="C74" t="n">
-        <v>9.22841682466233</v>
+        <v>9.25979686301714</v>
       </c>
     </row>
     <row r="75">
@@ -1575,7 +1575,7 @@
         <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>6.43827227328214</v>
+        <v>6.78410818134828</v>
       </c>
     </row>
     <row r="76">
@@ -1586,7 +1586,7 @@
         <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>6.43827227328214</v>
+        <v>6.78410818134828</v>
       </c>
     </row>
     <row r="77">
@@ -1597,7 +1597,7 @@
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>2.1996824357861</v>
+        <v>2.16944583764421</v>
       </c>
     </row>
     <row r="78">
@@ -1608,7 +1608,7 @@
         <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>2.1996824357861</v>
+        <v>2.16944583764421</v>
       </c>
     </row>
     <row r="79">
@@ -1619,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>2.51233871275674</v>
+        <v>2.49552581992415</v>
       </c>
     </row>
     <row r="80">
@@ -1630,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>2.51233871275674</v>
+        <v>2.49552581992415</v>
       </c>
     </row>
     <row r="81">
@@ -1641,7 +1641,7 @@
         <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>4.4358300437397</v>
+        <v>4.43710556758998</v>
       </c>
     </row>
     <row r="82">
@@ -1652,7 +1652,7 @@
         <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>4.4358300437397</v>
+        <v>4.43710556758999</v>
       </c>
     </row>
     <row r="83">
@@ -1663,7 +1663,7 @@
         <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>-10.1871446959223</v>
+        <v>-10.5821690339724</v>
       </c>
     </row>
     <row r="84">
@@ -1674,7 +1674,7 @@
         <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>-10.1871446959219</v>
+        <v>-10.5821690339723</v>
       </c>
     </row>
     <row r="85">
@@ -1685,7 +1685,7 @@
         <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>2.23383168486604</v>
+        <v>1.98134305749219</v>
       </c>
     </row>
     <row r="86">
@@ -1696,7 +1696,7 @@
         <v>4</v>
       </c>
       <c r="C86" t="n">
-        <v>2.23383168486604</v>
+        <v>1.98134305749219</v>
       </c>
     </row>
     <row r="87">
@@ -1707,7 +1707,7 @@
         <v>4</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.664546207661824</v>
+        <v>-0.66435795033167</v>
       </c>
     </row>
     <row r="88">
@@ -1718,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.664546207661826</v>
+        <v>-0.664357950331671</v>
       </c>
     </row>
     <row r="89">
@@ -1729,7 +1729,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>2.47411042756224</v>
+        <v>2.47456549912939</v>
       </c>
     </row>
     <row r="90">
@@ -1740,7 +1740,7 @@
         <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>2.47411042756224</v>
+        <v>2.47456549912938</v>
       </c>
     </row>
     <row r="91">
@@ -1751,7 +1751,7 @@
         <v>4</v>
       </c>
       <c r="C91" t="n">
-        <v>16.4218761825449</v>
+        <v>16.6088988410897</v>
       </c>
     </row>
     <row r="92">
@@ -1762,7 +1762,7 @@
         <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>16.4218761825449</v>
+        <v>16.6088988410897</v>
       </c>
     </row>
     <row r="93">
@@ -1773,7 +1773,7 @@
         <v>4</v>
       </c>
       <c r="C93" t="n">
-        <v>12.5888727271132</v>
+        <v>11.5798282809064</v>
       </c>
     </row>
     <row r="94">
@@ -1784,7 +1784,7 @@
         <v>4</v>
       </c>
       <c r="C94" t="n">
-        <v>12.5888727271132</v>
+        <v>11.5798282809064</v>
       </c>
     </row>
     <row r="95">
@@ -1795,7 +1795,7 @@
         <v>4</v>
       </c>
       <c r="C95" t="n">
-        <v>0.252829596764858</v>
+        <v>0.251630755758869</v>
       </c>
     </row>
     <row r="96">
@@ -1806,7 +1806,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="n">
-        <v>0.252829596764857</v>
+        <v>0.251630755758868</v>
       </c>
     </row>
     <row r="97">
@@ -1817,7 +1817,7 @@
         <v>4</v>
       </c>
       <c r="C97" t="n">
-        <v>7.37478377102132</v>
+        <v>7.37529819940036</v>
       </c>
     </row>
     <row r="98">
@@ -1828,7 +1828,7 @@
         <v>4</v>
       </c>
       <c r="C98" t="n">
-        <v>7.37478377102132</v>
+        <v>7.37529819940036</v>
       </c>
     </row>
     <row r="99">
@@ -1839,7 +1839,7 @@
         <v>4</v>
       </c>
       <c r="C99" t="n">
-        <v>1.77298331310007</v>
+        <v>1.77235748803335</v>
       </c>
     </row>
     <row r="100">
@@ -1850,7 +1850,7 @@
         <v>4</v>
       </c>
       <c r="C100" t="n">
-        <v>1.77298331310007</v>
+        <v>1.77235748803335</v>
       </c>
     </row>
     <row r="101">
@@ -1861,7 +1861,7 @@
         <v>4</v>
       </c>
       <c r="C101" t="n">
-        <v>0.174548980742532</v>
+        <v>0.174727936891033</v>
       </c>
     </row>
     <row r="102">
@@ -1872,7 +1872,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="n">
-        <v>0.174548980742532</v>
+        <v>0.174727936891033</v>
       </c>
     </row>
     <row r="103">
@@ -1883,7 +1883,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>7.2070761259635</v>
+        <v>7.20684904538553</v>
       </c>
     </row>
     <row r="104">
@@ -1894,7 +1894,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="n">
-        <v>7.2070761259635</v>
+        <v>7.20684904538553</v>
       </c>
     </row>
     <row r="105">
@@ -1905,7 +1905,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>1.004676147866</v>
+        <v>1.00450045881068</v>
       </c>
     </row>
     <row r="106">
@@ -1916,7 +1916,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>1.004676147866</v>
+        <v>1.00450045881068</v>
       </c>
     </row>
     <row r="107">
@@ -1927,7 +1927,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="n">
-        <v>4.28909721799728</v>
+        <v>4.14132329461224</v>
       </c>
     </row>
     <row r="108">
@@ -1938,7 +1938,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>4.28909721799728</v>
+        <v>4.14132329461224</v>
       </c>
     </row>
     <row r="109">
@@ -1949,7 +1949,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="n">
-        <v>3.2584891927878</v>
+        <v>3.3171135614733</v>
       </c>
     </row>
     <row r="110">
@@ -1960,7 +1960,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>3.2584891927878</v>
+        <v>3.3171135614733</v>
       </c>
     </row>
     <row r="111">
@@ -1971,7 +1971,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="n">
-        <v>3.46625703766325</v>
+        <v>3.62270224266998</v>
       </c>
     </row>
     <row r="112">
@@ -1982,7 +1982,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>3.46625703766325</v>
+        <v>3.62270224266998</v>
       </c>
     </row>
     <row r="113">
@@ -1993,7 +1993,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>13.6543329574097</v>
+        <v>13.8116015538048</v>
       </c>
     </row>
     <row r="114">
@@ -2004,7 +2004,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="n">
-        <v>13.6543329574097</v>
+        <v>13.8116015538048</v>
       </c>
     </row>
     <row r="115">
@@ -2015,7 +2015,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>16.4207020886032</v>
+        <v>16.6564858232989</v>
       </c>
     </row>
     <row r="116">
@@ -2026,7 +2026,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="n">
-        <v>16.4207020886032</v>
+        <v>16.6564858232989</v>
       </c>
     </row>
     <row r="117">
@@ -2037,7 +2037,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>0.320540738385171</v>
+        <v>0.46368978881607</v>
       </c>
     </row>
     <row r="118">
@@ -2048,7 +2048,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>0.320540738385171</v>
+        <v>0.463689788816071</v>
       </c>
     </row>
     <row r="119">
@@ -2059,7 +2059,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>5.18284830037465</v>
+        <v>4.19313242939553</v>
       </c>
     </row>
     <row r="120">
@@ -2070,7 +2070,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="n">
-        <v>5.18284830037465</v>
+        <v>4.19313242939553</v>
       </c>
     </row>
     <row r="121">
@@ -2081,7 +2081,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="n">
-        <v>-2.82360964163951</v>
+        <v>-2.82431441042732</v>
       </c>
     </row>
     <row r="122">
@@ -2092,7 +2092,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="n">
-        <v>-2.82360964163951</v>
+        <v>-2.82431441042732</v>
       </c>
     </row>
     <row r="123">
@@ -2103,7 +2103,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="n">
-        <v>10.8005922632227</v>
+        <v>10.7980521095364</v>
       </c>
     </row>
     <row r="124">
@@ -2114,7 +2114,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="n">
-        <v>10.8005922632227</v>
+        <v>10.7980521095364</v>
       </c>
     </row>
     <row r="125">
@@ -2125,7 +2125,7 @@
         <v>33</v>
       </c>
       <c r="C125" t="n">
-        <v>0.202544678355585</v>
+        <v>0.205362209623963</v>
       </c>
     </row>
     <row r="126">
@@ -2136,7 +2136,7 @@
         <v>33</v>
       </c>
       <c r="C126" t="n">
-        <v>0.202544678355585</v>
+        <v>0.205362209623963</v>
       </c>
     </row>
     <row r="127">
@@ -2147,7 +2147,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="n">
-        <v>1.84471536408702</v>
+        <v>1.84770316050052</v>
       </c>
     </row>
     <row r="128">
@@ -2158,7 +2158,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="n">
-        <v>1.84471536408702</v>
+        <v>1.84770316050052</v>
       </c>
     </row>
     <row r="129">
@@ -2169,7 +2169,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="n">
-        <v>6.17281251617355</v>
+        <v>6.74392287889956</v>
       </c>
     </row>
     <row r="130">
@@ -2180,7 +2180,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="n">
-        <v>6.17281251617355</v>
+        <v>6.74392287889956</v>
       </c>
     </row>
     <row r="131">
@@ -2191,7 +2191,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="n">
-        <v>4.06385953609146</v>
+        <v>4.73613926790511</v>
       </c>
     </row>
     <row r="132">
@@ -2202,7 +2202,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="n">
-        <v>4.06385953609146</v>
+        <v>4.73613926790511</v>
       </c>
     </row>
     <row r="133">
@@ -2213,7 +2213,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>0.9091030094148</v>
+        <v>0.994377375676674</v>
       </c>
     </row>
   </sheetData>

--- a/Zinc/4. Exploratory data analysis/Normality_checks.xlsx
+++ b/Zinc/4. Exploratory data analysis/Normality_checks.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -29,10 +29,7 @@
     <t xml:space="preserve">Fail</t>
   </si>
   <si>
-    <t xml:space="preserve">Dist_from_EFPC_km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drainage_area_km2</t>
+    <t xml:space="preserve">Upstream_from_main_stem_km</t>
   </si>
   <si>
     <t xml:space="preserve">Developed_lulc</t>
@@ -437,10 +434,10 @@
     <t xml:space="preserve">TBL_Zn_nmol_g</t>
   </si>
   <si>
+    <t xml:space="preserve">TBL_Zn_umol_g</t>
+  </si>
+  <si>
     <t xml:space="preserve">TBL_Zn_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBL_Zn_umol_g</t>
   </si>
   <si>
     <t xml:space="preserve">rel_prop_Zn</t>
@@ -813,7 +810,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>2.00686335405664</v>
+        <v>-0.866162986482195</v>
       </c>
     </row>
     <row r="5">
@@ -824,7 +821,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.866162986482195</v>
+        <v>0.262112805386116</v>
       </c>
     </row>
     <row r="6">
@@ -835,7 +832,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.262112805386116</v>
+        <v>0.189389410759909</v>
       </c>
     </row>
     <row r="7">
@@ -846,7 +843,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.189389410759909</v>
+        <v>3.92701712304009</v>
       </c>
     </row>
     <row r="8">
@@ -857,7 +854,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3.92701712304009</v>
+        <v>-0.534352395703904</v>
       </c>
     </row>
     <row r="9">
@@ -868,7 +865,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.534352395703904</v>
+        <v>-0.296160296305932</v>
       </c>
     </row>
     <row r="10">
@@ -879,7 +876,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.296160296305932</v>
+        <v>1.66356916338087</v>
       </c>
     </row>
     <row r="11">
@@ -890,7 +887,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>1.66356916338087</v>
+        <v>2.01866181190736</v>
       </c>
     </row>
     <row r="12">
@@ -901,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>2.01866181190736</v>
+        <v>1.11838120514126</v>
       </c>
     </row>
     <row r="13">
@@ -912,7 +909,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>1.11838120514126</v>
+        <v>2.1535439501211</v>
       </c>
     </row>
     <row r="14">
@@ -923,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1535439501211</v>
+        <v>-0.614198152259788</v>
       </c>
     </row>
     <row r="15">
@@ -934,7 +931,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.614198152259788</v>
+        <v>2.27374916500553</v>
       </c>
     </row>
     <row r="16">
@@ -945,7 +942,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>2.27374916500553</v>
+        <v>4.25239757909376</v>
       </c>
     </row>
     <row r="17">
@@ -956,7 +953,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>4.25239757909376</v>
+        <v>2.49729594453213</v>
       </c>
     </row>
     <row r="18">
@@ -967,7 +964,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>2.49729594453213</v>
+        <v>6.188471916066</v>
       </c>
     </row>
     <row r="19">
@@ -978,7 +975,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>6.188471916066</v>
+        <v>9.22841682466233</v>
       </c>
     </row>
     <row r="20">
@@ -989,7 +986,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>9.22841682466233</v>
+        <v>6.43827227328214</v>
       </c>
     </row>
     <row r="21">
@@ -1000,7 +997,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>6.43827227328214</v>
+        <v>2.1996824357861</v>
       </c>
     </row>
     <row r="22">
@@ -1011,7 +1008,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>2.1996824357861</v>
+        <v>2.51233871275674</v>
       </c>
     </row>
     <row r="23">
@@ -1022,7 +1019,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>2.51233871275674</v>
+        <v>4.4358300437397</v>
       </c>
     </row>
     <row r="24">
@@ -1033,7 +1030,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>4.4358300437397</v>
+        <v>-10.1871446959221</v>
       </c>
     </row>
     <row r="25">
@@ -1044,7 +1041,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>-10.1871446959221</v>
+        <v>2.23383168486604</v>
       </c>
     </row>
     <row r="26">
@@ -1055,7 +1052,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>2.23383168486604</v>
+        <v>5.18284830037465</v>
       </c>
     </row>
     <row r="27">
@@ -1066,7 +1063,7 @@
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>5.18284830037465</v>
+        <v>-2.82360964163951</v>
       </c>
     </row>
     <row r="28">
@@ -1077,7 +1074,7 @@
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>-2.82360964163951</v>
+        <v>10.8005922632227</v>
       </c>
     </row>
     <row r="29">
@@ -1085,21 +1082,21 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>10.8005922632227</v>
+        <v>0.202544678355585</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>0.202544678355585</v>
+        <v>1.84471536408702</v>
       </c>
     </row>
     <row r="31">
@@ -1110,7 +1107,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>1.84471536408702</v>
+        <v>6.17281251617355</v>
       </c>
     </row>
     <row r="32">
@@ -1121,7 +1118,7 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>6.17281251617355</v>
+        <v>-0.664546207661826</v>
       </c>
     </row>
     <row r="33">
@@ -1132,7 +1129,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.664546207661826</v>
+        <v>2.47411042756224</v>
       </c>
     </row>
     <row r="34">
@@ -1143,7 +1140,7 @@
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>2.47411042756224</v>
+        <v>16.4218761825449</v>
       </c>
     </row>
     <row r="35">
@@ -1154,7 +1151,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>16.4218761825449</v>
+        <v>12.5888727271131</v>
       </c>
     </row>
     <row r="36">
@@ -1165,7 +1162,7 @@
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>12.5888727271131</v>
+        <v>0.252829596764858</v>
       </c>
     </row>
     <row r="37">
@@ -1176,7 +1173,7 @@
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>0.252829596764858</v>
+        <v>7.37478377102132</v>
       </c>
     </row>
     <row r="38">
@@ -1187,7 +1184,7 @@
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>7.37478377102132</v>
+        <v>1.77298331310007</v>
       </c>
     </row>
     <row r="39">
@@ -1198,7 +1195,7 @@
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>1.77298331310007</v>
+        <v>0.174548980742531</v>
       </c>
     </row>
     <row r="40">
@@ -1209,7 +1206,7 @@
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>0.174548980742531</v>
+        <v>7.2070761259635</v>
       </c>
     </row>
     <row r="41">
@@ -1220,7 +1217,7 @@
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>7.2070761259635</v>
+        <v>1.004676147866</v>
       </c>
     </row>
     <row r="42">
@@ -1231,7 +1228,7 @@
         <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>1.004676147866</v>
+        <v>4.28909721799728</v>
       </c>
     </row>
     <row r="43">
@@ -1242,7 +1239,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>4.28909721799728</v>
+        <v>3.2584891927878</v>
       </c>
     </row>
     <row r="44">
@@ -1253,7 +1250,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="n">
-        <v>3.2584891927878</v>
+        <v>3.46625703766325</v>
       </c>
     </row>
     <row r="45">
@@ -1264,7 +1261,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>3.46625703766325</v>
+        <v>13.6543329574097</v>
       </c>
     </row>
     <row r="46">
@@ -1275,7 +1272,7 @@
         <v>4</v>
       </c>
       <c r="C46" t="n">
-        <v>13.6543329574097</v>
+        <v>16.4207020886032</v>
       </c>
     </row>
     <row r="47">
@@ -1286,7 +1283,7 @@
         <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>16.4207020886032</v>
+        <v>0.32054073838517</v>
       </c>
     </row>
     <row r="48">
@@ -1297,7 +1294,7 @@
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>0.32054073838517</v>
+        <v>3.92701712304009</v>
       </c>
     </row>
     <row r="49">
@@ -1319,7 +1316,7 @@
         <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>3.92701712304009</v>
+        <v>-0.534352395703903</v>
       </c>
     </row>
     <row r="51">
@@ -1330,7 +1327,7 @@
         <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.534352395703903</v>
+        <v>-0.534352395703905</v>
       </c>
     </row>
     <row r="52">
@@ -1341,7 +1338,7 @@
         <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.534352395703905</v>
+        <v>-0.296160296305932</v>
       </c>
     </row>
     <row r="53">
@@ -1352,7 +1349,7 @@
         <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.296160296305932</v>
+        <v>-0.296160296305931</v>
       </c>
     </row>
     <row r="54">
@@ -1363,7 +1360,7 @@
         <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.296160296305931</v>
+        <v>1.66356916338087</v>
       </c>
     </row>
     <row r="55">
@@ -1385,7 +1382,7 @@
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>1.66356916338087</v>
+        <v>2.01866181190736</v>
       </c>
     </row>
     <row r="57">
@@ -1407,7 +1404,7 @@
         <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>2.01866181190736</v>
+        <v>1.11838120514126</v>
       </c>
     </row>
     <row r="59">
@@ -1429,7 +1426,7 @@
         <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>1.11838120514126</v>
+        <v>2.1535439501211</v>
       </c>
     </row>
     <row r="61">
@@ -1451,7 +1448,7 @@
         <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>2.1535439501211</v>
+        <v>-0.614198152259787</v>
       </c>
     </row>
     <row r="63">
@@ -1473,7 +1470,7 @@
         <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.614198152259787</v>
+        <v>2.27374916500553</v>
       </c>
     </row>
     <row r="65">
@@ -1495,7 +1492,7 @@
         <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>2.27374916500553</v>
+        <v>4.25239757909376</v>
       </c>
     </row>
     <row r="67">
@@ -1517,7 +1514,7 @@
         <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>4.25239757909376</v>
+        <v>2.49729594453213</v>
       </c>
     </row>
     <row r="69">
@@ -1539,7 +1536,7 @@
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>2.49729594453213</v>
+        <v>6.188471916066</v>
       </c>
     </row>
     <row r="71">
@@ -1561,7 +1558,7 @@
         <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>6.188471916066</v>
+        <v>9.22841682466233</v>
       </c>
     </row>
     <row r="73">
@@ -1583,7 +1580,7 @@
         <v>4</v>
       </c>
       <c r="C74" t="n">
-        <v>9.22841682466233</v>
+        <v>6.43827227328214</v>
       </c>
     </row>
     <row r="75">
@@ -1605,7 +1602,7 @@
         <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>6.43827227328214</v>
+        <v>2.1996824357861</v>
       </c>
     </row>
     <row r="77">
@@ -1627,7 +1624,7 @@
         <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>2.1996824357861</v>
+        <v>2.51233871275674</v>
       </c>
     </row>
     <row r="79">
@@ -1649,7 +1646,7 @@
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>2.51233871275674</v>
+        <v>4.4358300437397</v>
       </c>
     </row>
     <row r="81">
@@ -1671,7 +1668,7 @@
         <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>4.4358300437397</v>
+        <v>-10.1871446959223</v>
       </c>
     </row>
     <row r="83">
@@ -1682,7 +1679,7 @@
         <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>-10.1871446959223</v>
+        <v>-10.1871446959219</v>
       </c>
     </row>
     <row r="84">
@@ -1693,7 +1690,7 @@
         <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>-10.1871446959219</v>
+        <v>2.23383168486604</v>
       </c>
     </row>
     <row r="85">
@@ -1715,7 +1712,7 @@
         <v>4</v>
       </c>
       <c r="C86" t="n">
-        <v>2.23383168486604</v>
+        <v>-0.664546207661824</v>
       </c>
     </row>
     <row r="87">
@@ -1726,7 +1723,7 @@
         <v>4</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.664546207661824</v>
+        <v>-0.664546207661826</v>
       </c>
     </row>
     <row r="88">
@@ -1737,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.664546207661826</v>
+        <v>2.47411042756224</v>
       </c>
     </row>
     <row r="89">
@@ -1759,7 +1756,7 @@
         <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>2.47411042756224</v>
+        <v>16.4218761825449</v>
       </c>
     </row>
     <row r="91">
@@ -1781,7 +1778,7 @@
         <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>16.4218761825449</v>
+        <v>12.5888727271132</v>
       </c>
     </row>
     <row r="93">
@@ -1803,7 +1800,7 @@
         <v>4</v>
       </c>
       <c r="C94" t="n">
-        <v>12.5888727271132</v>
+        <v>0.252829596764858</v>
       </c>
     </row>
     <row r="95">
@@ -1814,7 +1811,7 @@
         <v>4</v>
       </c>
       <c r="C95" t="n">
-        <v>0.252829596764858</v>
+        <v>0.252829596764857</v>
       </c>
     </row>
     <row r="96">
@@ -1825,7 +1822,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="n">
-        <v>0.252829596764857</v>
+        <v>7.37478377102132</v>
       </c>
     </row>
     <row r="97">
@@ -1847,7 +1844,7 @@
         <v>4</v>
       </c>
       <c r="C98" t="n">
-        <v>7.37478377102132</v>
+        <v>1.77298331310007</v>
       </c>
     </row>
     <row r="99">
@@ -1869,7 +1866,7 @@
         <v>4</v>
       </c>
       <c r="C100" t="n">
-        <v>1.77298331310007</v>
+        <v>0.174548980742532</v>
       </c>
     </row>
     <row r="101">
@@ -1891,7 +1888,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="n">
-        <v>0.174548980742532</v>
+        <v>7.2070761259635</v>
       </c>
     </row>
     <row r="103">
@@ -1913,7 +1910,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="n">
-        <v>7.2070761259635</v>
+        <v>1.004676147866</v>
       </c>
     </row>
     <row r="105">
@@ -1935,7 +1932,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>1.004676147866</v>
+        <v>4.28909721799728</v>
       </c>
     </row>
     <row r="107">
@@ -1957,7 +1954,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>4.28909721799728</v>
+        <v>3.2584891927878</v>
       </c>
     </row>
     <row r="109">
@@ -1979,7 +1976,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>3.2584891927878</v>
+        <v>3.46625703766325</v>
       </c>
     </row>
     <row r="111">
@@ -2001,7 +1998,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>3.46625703766325</v>
+        <v>13.6543329574097</v>
       </c>
     </row>
     <row r="113">
@@ -2023,7 +2020,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="n">
-        <v>13.6543329574097</v>
+        <v>16.4207020886032</v>
       </c>
     </row>
     <row r="115">
@@ -2045,7 +2042,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="n">
-        <v>16.4207020886032</v>
+        <v>0.320540738385171</v>
       </c>
     </row>
     <row r="117">
@@ -2067,7 +2064,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>0.320540738385171</v>
+        <v>5.18284830037465</v>
       </c>
     </row>
     <row r="119">
@@ -2100,7 +2097,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="n">
-        <v>5.18284830037465</v>
+        <v>-2.82360964163951</v>
       </c>
     </row>
     <row r="122">
@@ -2133,7 +2130,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="n">
-        <v>-2.82360964163951</v>
+        <v>10.8005922632227</v>
       </c>
     </row>
     <row r="125">
@@ -2163,10 +2160,10 @@
         <v>130</v>
       </c>
       <c r="B127" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C127" t="n">
-        <v>10.8005922632227</v>
+        <v>0.202544678355585</v>
       </c>
     </row>
     <row r="128">
@@ -2174,7 +2171,7 @@
         <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C128" t="n">
         <v>0.202544678355585</v>
@@ -2185,7 +2182,7 @@
         <v>132</v>
       </c>
       <c r="B129" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C129" t="n">
         <v>0.202544678355585</v>
@@ -2196,10 +2193,10 @@
         <v>133</v>
       </c>
       <c r="B130" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C130" t="n">
-        <v>0.202544678355585</v>
+        <v>1.84471536408702</v>
       </c>
     </row>
     <row r="131">
@@ -2221,7 +2218,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="n">
-        <v>1.84471536408702</v>
+        <v>1.84471536408701</v>
       </c>
     </row>
     <row r="133">
@@ -2232,7 +2229,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>1.84471536408701</v>
+        <v>6.17281251617355</v>
       </c>
     </row>
     <row r="134">
@@ -2265,7 +2262,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="n">
-        <v>6.17281251617355</v>
+        <v>4.06385953609146</v>
       </c>
     </row>
     <row r="137">
@@ -2298,17 +2295,6 @@
         <v>4</v>
       </c>
       <c r="C139" t="n">
-        <v>4.06385953609146</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>143</v>
-      </c>
-      <c r="B140" t="s">
-        <v>4</v>
-      </c>
-      <c r="C140" t="n">
         <v>0.9091030094148</v>
       </c>
     </row>

--- a/Zinc/4. Exploratory data analysis/Normality_checks.xlsx
+++ b/Zinc/4. Exploratory data analysis/Normality_checks.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -23,10 +23,13 @@
     <t xml:space="preserve">Skewness</t>
   </si>
   <si>
+    <t xml:space="preserve">Elevation_m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fail</t>
+  </si>
+  <si>
     <t xml:space="preserve">Relative_elevation_m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fail</t>
   </si>
   <si>
     <t xml:space="preserve">Upstream_from_main_stem_km</t>
@@ -788,7 +791,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>2.17301857884221</v>
+        <v>-0.215974881892846</v>
       </c>
     </row>
     <row r="3">
@@ -799,7 +802,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>0.781738678603504</v>
+        <v>2.17301857884221</v>
       </c>
     </row>
     <row r="4">
@@ -810,7 +813,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.866162986482195</v>
+        <v>0.781738678603504</v>
       </c>
     </row>
     <row r="5">
@@ -821,7 +824,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.262112805386116</v>
+        <v>-0.866162986482195</v>
       </c>
     </row>
     <row r="6">
@@ -832,7 +835,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.189389410759909</v>
+        <v>0.262112805386116</v>
       </c>
     </row>
     <row r="7">
@@ -843,7 +846,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>3.92701712304009</v>
+        <v>0.189389410759909</v>
       </c>
     </row>
     <row r="8">
@@ -854,7 +857,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.534352395703904</v>
+        <v>3.92701712304009</v>
       </c>
     </row>
     <row r="9">
@@ -865,7 +868,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.296160296305932</v>
+        <v>-0.534352395703904</v>
       </c>
     </row>
     <row r="10">
@@ -876,7 +879,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>1.66356916338087</v>
+        <v>-0.296160296305932</v>
       </c>
     </row>
     <row r="11">
@@ -887,7 +890,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>2.01866181190736</v>
+        <v>1.66356916338087</v>
       </c>
     </row>
     <row r="12">
@@ -898,7 +901,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>1.11838120514126</v>
+        <v>2.01866181190736</v>
       </c>
     </row>
     <row r="13">
@@ -909,7 +912,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>2.1535439501211</v>
+        <v>1.11838120514126</v>
       </c>
     </row>
     <row r="14">
@@ -920,7 +923,7 @@
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.614198152259788</v>
+        <v>2.1535439501211</v>
       </c>
     </row>
     <row r="15">
@@ -931,7 +934,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>2.27374916500553</v>
+        <v>-0.614198152259788</v>
       </c>
     </row>
     <row r="16">
@@ -942,7 +945,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>4.25239757909376</v>
+        <v>2.27374916500553</v>
       </c>
     </row>
     <row r="17">
@@ -953,7 +956,7 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>2.49729594453213</v>
+        <v>4.25239757909376</v>
       </c>
     </row>
     <row r="18">
@@ -964,7 +967,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>6.188471916066</v>
+        <v>2.49729594453213</v>
       </c>
     </row>
     <row r="19">
@@ -975,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>9.22841682466233</v>
+        <v>6.188471916066</v>
       </c>
     </row>
     <row r="20">
@@ -986,7 +989,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>6.43827227328214</v>
+        <v>9.22841682466233</v>
       </c>
     </row>
     <row r="21">
@@ -997,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>2.1996824357861</v>
+        <v>6.43827227328214</v>
       </c>
     </row>
     <row r="22">
@@ -1008,7 +1011,7 @@
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>2.51233871275674</v>
+        <v>2.1996824357861</v>
       </c>
     </row>
     <row r="23">
@@ -1019,7 +1022,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>4.4358300437397</v>
+        <v>2.51233871275674</v>
       </c>
     </row>
     <row r="24">
@@ -1030,7 +1033,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>-10.1871446959221</v>
+        <v>4.4358300437397</v>
       </c>
     </row>
     <row r="25">
@@ -1041,7 +1044,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>2.23383168486604</v>
+        <v>-10.1871446959221</v>
       </c>
     </row>
     <row r="26">
@@ -1052,7 +1055,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>5.18284830037465</v>
+        <v>2.23383168486604</v>
       </c>
     </row>
     <row r="27">
@@ -1063,7 +1066,7 @@
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>-2.82360964163951</v>
+        <v>5.18284830037465</v>
       </c>
     </row>
     <row r="28">
@@ -1074,7 +1077,7 @@
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>10.8005922632227</v>
+        <v>-2.82360964163951</v>
       </c>
     </row>
     <row r="29">
@@ -1082,21 +1085,21 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>0.202544678355585</v>
+        <v>10.8005922632227</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
         <v>33</v>
       </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
       <c r="C30" t="n">
-        <v>1.84471536408702</v>
+        <v>0.202544678355585</v>
       </c>
     </row>
     <row r="31">
@@ -1107,7 +1110,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>6.17281251617355</v>
+        <v>1.84471536408702</v>
       </c>
     </row>
     <row r="32">
@@ -1118,7 +1121,7 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.664546207661826</v>
+        <v>6.17281251617355</v>
       </c>
     </row>
     <row r="33">
@@ -1129,7 +1132,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>2.47411042756224</v>
+        <v>-0.664546207661826</v>
       </c>
     </row>
     <row r="34">
@@ -1140,7 +1143,7 @@
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>16.4218761825449</v>
+        <v>2.47411042756224</v>
       </c>
     </row>
     <row r="35">
@@ -1151,7 +1154,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>12.5888727271131</v>
+        <v>16.4218761825449</v>
       </c>
     </row>
     <row r="36">
@@ -1162,7 +1165,7 @@
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>0.252829596764858</v>
+        <v>12.5888727271131</v>
       </c>
     </row>
     <row r="37">
@@ -1173,7 +1176,7 @@
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>7.37478377102132</v>
+        <v>0.252829596764858</v>
       </c>
     </row>
     <row r="38">
@@ -1184,7 +1187,7 @@
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>1.77298331310007</v>
+        <v>7.37478377102132</v>
       </c>
     </row>
     <row r="39">
@@ -1195,7 +1198,7 @@
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>0.174548980742531</v>
+        <v>1.77298331310007</v>
       </c>
     </row>
     <row r="40">
@@ -1206,7 +1209,7 @@
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>7.2070761259635</v>
+        <v>0.174548980742531</v>
       </c>
     </row>
     <row r="41">
@@ -1217,7 +1220,7 @@
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>1.004676147866</v>
+        <v>7.2070761259635</v>
       </c>
     </row>
     <row r="42">
@@ -1228,7 +1231,7 @@
         <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>4.28909721799728</v>
+        <v>1.004676147866</v>
       </c>
     </row>
     <row r="43">
@@ -1239,7 +1242,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>3.2584891927878</v>
+        <v>4.28909721799728</v>
       </c>
     </row>
     <row r="44">
@@ -1250,7 +1253,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="n">
-        <v>3.46625703766325</v>
+        <v>3.2584891927878</v>
       </c>
     </row>
     <row r="45">
@@ -1261,7 +1264,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>13.6543329574097</v>
+        <v>3.46625703766325</v>
       </c>
     </row>
     <row r="46">
@@ -1272,7 +1275,7 @@
         <v>4</v>
       </c>
       <c r="C46" t="n">
-        <v>16.4207020886032</v>
+        <v>13.6543329574097</v>
       </c>
     </row>
     <row r="47">
@@ -1283,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>0.32054073838517</v>
+        <v>16.4207020886032</v>
       </c>
     </row>
     <row r="48">
@@ -1294,7 +1297,7 @@
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>3.92701712304009</v>
+        <v>0.32054073838517</v>
       </c>
     </row>
     <row r="49">
@@ -1316,7 +1319,7 @@
         <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.534352395703903</v>
+        <v>3.92701712304009</v>
       </c>
     </row>
     <row r="51">
@@ -1327,7 +1330,7 @@
         <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.534352395703905</v>
+        <v>-0.534352395703903</v>
       </c>
     </row>
     <row r="52">
@@ -1338,7 +1341,7 @@
         <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.296160296305932</v>
+        <v>-0.534352395703905</v>
       </c>
     </row>
     <row r="53">
@@ -1349,7 +1352,7 @@
         <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.296160296305931</v>
+        <v>-0.296160296305932</v>
       </c>
     </row>
     <row r="54">
@@ -1360,7 +1363,7 @@
         <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>1.66356916338087</v>
+        <v>-0.296160296305931</v>
       </c>
     </row>
     <row r="55">
@@ -1382,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>2.01866181190736</v>
+        <v>1.66356916338087</v>
       </c>
     </row>
     <row r="57">
@@ -1404,7 +1407,7 @@
         <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>1.11838120514126</v>
+        <v>2.01866181190736</v>
       </c>
     </row>
     <row r="59">
@@ -1426,7 +1429,7 @@
         <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>2.1535439501211</v>
+        <v>1.11838120514126</v>
       </c>
     </row>
     <row r="61">
@@ -1448,7 +1451,7 @@
         <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.614198152259787</v>
+        <v>2.1535439501211</v>
       </c>
     </row>
     <row r="63">
@@ -1470,7 +1473,7 @@
         <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>2.27374916500553</v>
+        <v>-0.614198152259787</v>
       </c>
     </row>
     <row r="65">
@@ -1492,7 +1495,7 @@
         <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>4.25239757909376</v>
+        <v>2.27374916500553</v>
       </c>
     </row>
     <row r="67">
@@ -1514,7 +1517,7 @@
         <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>2.49729594453213</v>
+        <v>4.25239757909376</v>
       </c>
     </row>
     <row r="69">
@@ -1536,7 +1539,7 @@
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>6.188471916066</v>
+        <v>2.49729594453213</v>
       </c>
     </row>
     <row r="71">
@@ -1558,7 +1561,7 @@
         <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>9.22841682466233</v>
+        <v>6.188471916066</v>
       </c>
     </row>
     <row r="73">
@@ -1580,7 +1583,7 @@
         <v>4</v>
       </c>
       <c r="C74" t="n">
-        <v>6.43827227328214</v>
+        <v>9.22841682466233</v>
       </c>
     </row>
     <row r="75">
@@ -1602,7 +1605,7 @@
         <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>2.1996824357861</v>
+        <v>6.43827227328214</v>
       </c>
     </row>
     <row r="77">
@@ -1624,7 +1627,7 @@
         <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>2.51233871275674</v>
+        <v>2.1996824357861</v>
       </c>
     </row>
     <row r="79">
@@ -1646,7 +1649,7 @@
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>4.4358300437397</v>
+        <v>2.51233871275674</v>
       </c>
     </row>
     <row r="81">
@@ -1668,7 +1671,7 @@
         <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>-10.1871446959223</v>
+        <v>4.4358300437397</v>
       </c>
     </row>
     <row r="83">
@@ -1679,7 +1682,7 @@
         <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>-10.1871446959219</v>
+        <v>-10.1871446959223</v>
       </c>
     </row>
     <row r="84">
@@ -1690,7 +1693,7 @@
         <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>2.23383168486604</v>
+        <v>-10.1871446959219</v>
       </c>
     </row>
     <row r="85">
@@ -1712,7 +1715,7 @@
         <v>4</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.664546207661824</v>
+        <v>2.23383168486604</v>
       </c>
     </row>
     <row r="87">
@@ -1723,7 +1726,7 @@
         <v>4</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.664546207661826</v>
+        <v>-0.664546207661824</v>
       </c>
     </row>
     <row r="88">
@@ -1734,7 +1737,7 @@
         <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>2.47411042756224</v>
+        <v>-0.664546207661826</v>
       </c>
     </row>
     <row r="89">
@@ -1756,7 +1759,7 @@
         <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>16.4218761825449</v>
+        <v>2.47411042756224</v>
       </c>
     </row>
     <row r="91">
@@ -1778,7 +1781,7 @@
         <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>12.5888727271132</v>
+        <v>16.4218761825449</v>
       </c>
     </row>
     <row r="93">
@@ -1800,7 +1803,7 @@
         <v>4</v>
       </c>
       <c r="C94" t="n">
-        <v>0.252829596764858</v>
+        <v>12.5888727271132</v>
       </c>
     </row>
     <row r="95">
@@ -1811,7 +1814,7 @@
         <v>4</v>
       </c>
       <c r="C95" t="n">
-        <v>0.252829596764857</v>
+        <v>0.252829596764858</v>
       </c>
     </row>
     <row r="96">
@@ -1822,7 +1825,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="n">
-        <v>7.37478377102132</v>
+        <v>0.252829596764857</v>
       </c>
     </row>
     <row r="97">
@@ -1844,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="C98" t="n">
-        <v>1.77298331310007</v>
+        <v>7.37478377102132</v>
       </c>
     </row>
     <row r="99">
@@ -1866,7 +1869,7 @@
         <v>4</v>
       </c>
       <c r="C100" t="n">
-        <v>0.174548980742532</v>
+        <v>1.77298331310007</v>
       </c>
     </row>
     <row r="101">
@@ -1888,7 +1891,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="n">
-        <v>7.2070761259635</v>
+        <v>0.174548980742532</v>
       </c>
     </row>
     <row r="103">
@@ -1910,7 +1913,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="n">
-        <v>1.004676147866</v>
+        <v>7.2070761259635</v>
       </c>
     </row>
     <row r="105">
@@ -1932,7 +1935,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>4.28909721799728</v>
+        <v>1.004676147866</v>
       </c>
     </row>
     <row r="107">
@@ -1954,7 +1957,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="n">
-        <v>3.2584891927878</v>
+        <v>4.28909721799728</v>
       </c>
     </row>
     <row r="109">
@@ -1976,7 +1979,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>3.46625703766325</v>
+        <v>3.2584891927878</v>
       </c>
     </row>
     <row r="111">
@@ -1998,7 +2001,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>13.6543329574097</v>
+        <v>3.46625703766325</v>
       </c>
     </row>
     <row r="113">
@@ -2020,7 +2023,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="n">
-        <v>16.4207020886032</v>
+        <v>13.6543329574097</v>
       </c>
     </row>
     <row r="115">
@@ -2042,7 +2045,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="n">
-        <v>0.320540738385171</v>
+        <v>16.4207020886032</v>
       </c>
     </row>
     <row r="117">
@@ -2064,7 +2067,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>5.18284830037465</v>
+        <v>0.320540738385171</v>
       </c>
     </row>
     <row r="119">
@@ -2097,7 +2100,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="n">
-        <v>-2.82360964163951</v>
+        <v>5.18284830037465</v>
       </c>
     </row>
     <row r="122">
@@ -2130,7 +2133,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="n">
-        <v>10.8005922632227</v>
+        <v>-2.82360964163951</v>
       </c>
     </row>
     <row r="125">
@@ -2160,10 +2163,10 @@
         <v>130</v>
       </c>
       <c r="B127" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.202544678355585</v>
+        <v>10.8005922632227</v>
       </c>
     </row>
     <row r="128">
@@ -2171,7 +2174,7 @@
         <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C128" t="n">
         <v>0.202544678355585</v>
@@ -2182,7 +2185,7 @@
         <v>132</v>
       </c>
       <c r="B129" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C129" t="n">
         <v>0.202544678355585</v>
@@ -2193,10 +2196,10 @@
         <v>133</v>
       </c>
       <c r="B130" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C130" t="n">
-        <v>1.84471536408702</v>
+        <v>0.202544678355585</v>
       </c>
     </row>
     <row r="131">
@@ -2218,7 +2221,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="n">
-        <v>1.84471536408701</v>
+        <v>1.84471536408702</v>
       </c>
     </row>
     <row r="133">
@@ -2229,7 +2232,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>6.17281251617355</v>
+        <v>1.84471536408701</v>
       </c>
     </row>
     <row r="134">
@@ -2262,7 +2265,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="n">
-        <v>4.06385953609146</v>
+        <v>6.17281251617355</v>
       </c>
     </row>
     <row r="137">
@@ -2295,6 +2298,17 @@
         <v>4</v>
       </c>
       <c r="C139" t="n">
+        <v>4.06385953609146</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" t="n">
         <v>0.9091030094148</v>
       </c>
     </row>

--- a/Zinc/4. Exploratory data analysis/Normality_checks.xlsx
+++ b/Zinc/4. Exploratory data analysis/Normality_checks.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
@@ -167,7 +167,10 @@
     <t xml:space="preserve">TOrg_K_M</t>
   </si>
   <si>
-    <t xml:space="preserve">Zn_Toxicity_Daphnia_M</t>
+    <t xml:space="preserve">Zn_chronic_tox_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_acute_tox_M</t>
   </si>
   <si>
     <t xml:space="preserve">DOC_M</t>
@@ -374,10 +377,16 @@
     <t xml:space="preserve">TOrg_K_nM</t>
   </si>
   <si>
-    <t xml:space="preserve">Zn_Toxicity_Daphnia_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn_Toxicity_Daphnia_nM</t>
+    <t xml:space="preserve">Zn_chronic_tox_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_chronic_tox_nM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_acute_tox_uM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn_acute_tox_nM</t>
   </si>
   <si>
     <t xml:space="preserve">BL_Zn_nmol_kg</t>
@@ -1297,7 +1306,7 @@
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>0.32054073838517</v>
+        <v>1.09014872856816</v>
       </c>
     </row>
     <row r="49">
@@ -1308,7 +1317,7 @@
         <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>3.92701712304009</v>
+        <v>0.527955794767177</v>
       </c>
     </row>
     <row r="50">
@@ -1330,7 +1339,7 @@
         <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.534352395703903</v>
+        <v>3.92701712304009</v>
       </c>
     </row>
     <row r="52">
@@ -1341,7 +1350,7 @@
         <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.534352395703905</v>
+        <v>-0.534352395703903</v>
       </c>
     </row>
     <row r="53">
@@ -1352,7 +1361,7 @@
         <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.296160296305932</v>
+        <v>-0.534352395703905</v>
       </c>
     </row>
     <row r="54">
@@ -1363,7 +1372,7 @@
         <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.296160296305931</v>
+        <v>-0.296160296305932</v>
       </c>
     </row>
     <row r="55">
@@ -1374,7 +1383,7 @@
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>1.66356916338087</v>
+        <v>-0.296160296305931</v>
       </c>
     </row>
     <row r="56">
@@ -1396,7 +1405,7 @@
         <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>2.01866181190736</v>
+        <v>1.66356916338087</v>
       </c>
     </row>
     <row r="58">
@@ -1418,7 +1427,7 @@
         <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>1.11838120514126</v>
+        <v>2.01866181190736</v>
       </c>
     </row>
     <row r="60">
@@ -1440,7 +1449,7 @@
         <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>2.1535439501211</v>
+        <v>1.11838120514126</v>
       </c>
     </row>
     <row r="62">
@@ -1462,7 +1471,7 @@
         <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.614198152259787</v>
+        <v>2.1535439501211</v>
       </c>
     </row>
     <row r="64">
@@ -1484,7 +1493,7 @@
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>2.27374916500553</v>
+        <v>-0.614198152259787</v>
       </c>
     </row>
     <row r="66">
@@ -1506,7 +1515,7 @@
         <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>4.25239757909376</v>
+        <v>2.27374916500553</v>
       </c>
     </row>
     <row r="68">
@@ -1528,7 +1537,7 @@
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>2.49729594453213</v>
+        <v>4.25239757909376</v>
       </c>
     </row>
     <row r="70">
@@ -1550,7 +1559,7 @@
         <v>4</v>
       </c>
       <c r="C71" t="n">
-        <v>6.188471916066</v>
+        <v>2.49729594453213</v>
       </c>
     </row>
     <row r="72">
@@ -1572,7 +1581,7 @@
         <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>9.22841682466233</v>
+        <v>6.188471916066</v>
       </c>
     </row>
     <row r="74">
@@ -1594,7 +1603,7 @@
         <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>6.43827227328214</v>
+        <v>9.22841682466233</v>
       </c>
     </row>
     <row r="76">
@@ -1616,7 +1625,7 @@
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>2.1996824357861</v>
+        <v>6.43827227328214</v>
       </c>
     </row>
     <row r="78">
@@ -1638,7 +1647,7 @@
         <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>2.51233871275674</v>
+        <v>2.1996824357861</v>
       </c>
     </row>
     <row r="80">
@@ -1660,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>4.4358300437397</v>
+        <v>2.51233871275674</v>
       </c>
     </row>
     <row r="82">
@@ -1682,7 +1691,7 @@
         <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>-10.1871446959223</v>
+        <v>4.4358300437397</v>
       </c>
     </row>
     <row r="84">
@@ -1693,7 +1702,7 @@
         <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>-10.1871446959219</v>
+        <v>-10.1871446959223</v>
       </c>
     </row>
     <row r="85">
@@ -1704,7 +1713,7 @@
         <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>2.23383168486604</v>
+        <v>-10.1871446959219</v>
       </c>
     </row>
     <row r="86">
@@ -1726,7 +1735,7 @@
         <v>4</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.664546207661824</v>
+        <v>2.23383168486604</v>
       </c>
     </row>
     <row r="88">
@@ -1737,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.664546207661826</v>
+        <v>-0.664546207661824</v>
       </c>
     </row>
     <row r="89">
@@ -1748,7 +1757,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>2.47411042756224</v>
+        <v>-0.664546207661826</v>
       </c>
     </row>
     <row r="90">
@@ -1770,7 +1779,7 @@
         <v>4</v>
       </c>
       <c r="C91" t="n">
-        <v>16.4218761825449</v>
+        <v>2.47411042756224</v>
       </c>
     </row>
     <row r="92">
@@ -1792,7 +1801,7 @@
         <v>4</v>
       </c>
       <c r="C93" t="n">
-        <v>12.5888727271132</v>
+        <v>16.4218761825449</v>
       </c>
     </row>
     <row r="94">
@@ -1814,7 +1823,7 @@
         <v>4</v>
       </c>
       <c r="C95" t="n">
-        <v>0.252829596764858</v>
+        <v>12.5888727271132</v>
       </c>
     </row>
     <row r="96">
@@ -1825,7 +1834,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="n">
-        <v>0.252829596764857</v>
+        <v>0.252829596764858</v>
       </c>
     </row>
     <row r="97">
@@ -1836,7 +1845,7 @@
         <v>4</v>
       </c>
       <c r="C97" t="n">
-        <v>7.37478377102132</v>
+        <v>0.252829596764857</v>
       </c>
     </row>
     <row r="98">
@@ -1858,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="C99" t="n">
-        <v>1.77298331310007</v>
+        <v>7.37478377102132</v>
       </c>
     </row>
     <row r="100">
@@ -1880,7 +1889,7 @@
         <v>4</v>
       </c>
       <c r="C101" t="n">
-        <v>0.174548980742532</v>
+        <v>1.77298331310007</v>
       </c>
     </row>
     <row r="102">
@@ -1902,7 +1911,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>7.2070761259635</v>
+        <v>0.174548980742532</v>
       </c>
     </row>
     <row r="104">
@@ -1924,7 +1933,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>1.004676147866</v>
+        <v>7.2070761259635</v>
       </c>
     </row>
     <row r="106">
@@ -1946,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="n">
-        <v>4.28909721799728</v>
+        <v>1.004676147866</v>
       </c>
     </row>
     <row r="108">
@@ -1968,7 +1977,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="n">
-        <v>3.2584891927878</v>
+        <v>4.28909721799728</v>
       </c>
     </row>
     <row r="110">
@@ -1990,7 +1999,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="n">
-        <v>3.46625703766325</v>
+        <v>3.2584891927878</v>
       </c>
     </row>
     <row r="112">
@@ -2012,7 +2021,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>13.6543329574097</v>
+        <v>3.46625703766325</v>
       </c>
     </row>
     <row r="114">
@@ -2034,7 +2043,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="n">
-        <v>16.4207020886032</v>
+        <v>13.6543329574097</v>
       </c>
     </row>
     <row r="116">
@@ -2056,7 +2065,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="n">
-        <v>0.320540738385171</v>
+        <v>16.4207020886032</v>
       </c>
     </row>
     <row r="118">
@@ -2067,7 +2076,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="n">
-        <v>0.320540738385171</v>
+        <v>1.09014872856816</v>
       </c>
     </row>
     <row r="119">
@@ -2078,7 +2087,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="n">
-        <v>5.18284830037465</v>
+        <v>1.09014872856815</v>
       </c>
     </row>
     <row r="120">
@@ -2089,7 +2098,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="n">
-        <v>5.18284830037465</v>
+        <v>0.527955794767177</v>
       </c>
     </row>
     <row r="121">
@@ -2100,7 +2109,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="n">
-        <v>5.18284830037465</v>
+        <v>0.527955794767177</v>
       </c>
     </row>
     <row r="122">
@@ -2111,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="n">
-        <v>-2.82360964163951</v>
+        <v>5.18284830037465</v>
       </c>
     </row>
     <row r="123">
@@ -2122,7 +2131,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="n">
-        <v>-2.82360964163951</v>
+        <v>5.18284830037465</v>
       </c>
     </row>
     <row r="124">
@@ -2133,7 +2142,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="n">
-        <v>-2.82360964163951</v>
+        <v>5.18284830037465</v>
       </c>
     </row>
     <row r="125">
@@ -2144,7 +2153,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>10.8005922632227</v>
+        <v>-2.82360964163951</v>
       </c>
     </row>
     <row r="126">
@@ -2155,7 +2164,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="n">
-        <v>10.8005922632227</v>
+        <v>-2.82360964163951</v>
       </c>
     </row>
     <row r="127">
@@ -2166,7 +2175,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="n">
-        <v>10.8005922632227</v>
+        <v>-2.82360964163951</v>
       </c>
     </row>
     <row r="128">
@@ -2174,10 +2183,10 @@
         <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C128" t="n">
-        <v>0.202544678355585</v>
+        <v>10.8005922632227</v>
       </c>
     </row>
     <row r="129">
@@ -2185,10 +2194,10 @@
         <v>132</v>
       </c>
       <c r="B129" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C129" t="n">
-        <v>0.202544678355585</v>
+        <v>10.8005922632227</v>
       </c>
     </row>
     <row r="130">
@@ -2196,10 +2205,10 @@
         <v>133</v>
       </c>
       <c r="B130" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C130" t="n">
-        <v>0.202544678355585</v>
+        <v>10.8005922632227</v>
       </c>
     </row>
     <row r="131">
@@ -2207,10 +2216,10 @@
         <v>134</v>
       </c>
       <c r="B131" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C131" t="n">
-        <v>1.84471536408702</v>
+        <v>0.202544678355585</v>
       </c>
     </row>
     <row r="132">
@@ -2218,10 +2227,10 @@
         <v>135</v>
       </c>
       <c r="B132" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C132" t="n">
-        <v>1.84471536408702</v>
+        <v>0.202544678355585</v>
       </c>
     </row>
     <row r="133">
@@ -2229,10 +2238,10 @@
         <v>136</v>
       </c>
       <c r="B133" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C133" t="n">
-        <v>1.84471536408701</v>
+        <v>0.202544678355585</v>
       </c>
     </row>
     <row r="134">
@@ -2243,7 +2252,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="n">
-        <v>6.17281251617355</v>
+        <v>1.84471536408702</v>
       </c>
     </row>
     <row r="135">
@@ -2254,7 +2263,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="n">
-        <v>6.17281251617355</v>
+        <v>1.84471536408702</v>
       </c>
     </row>
     <row r="136">
@@ -2265,7 +2274,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="n">
-        <v>6.17281251617355</v>
+        <v>1.84471536408701</v>
       </c>
     </row>
     <row r="137">
@@ -2276,7 +2285,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="n">
-        <v>4.06385953609146</v>
+        <v>6.17281251617355</v>
       </c>
     </row>
     <row r="138">
@@ -2287,7 +2296,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="n">
-        <v>4.06385953609146</v>
+        <v>6.17281251617355</v>
       </c>
     </row>
     <row r="139">
@@ -2298,7 +2307,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="n">
-        <v>4.06385953609146</v>
+        <v>6.17281251617355</v>
       </c>
     </row>
     <row r="140">
@@ -2309,6 +2318,39 @@
         <v>4</v>
       </c>
       <c r="C140" t="n">
+        <v>4.06385953609146</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141" t="s">
+        <v>4</v>
+      </c>
+      <c r="C141" t="n">
+        <v>4.06385953609146</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>145</v>
+      </c>
+      <c r="B142" t="s">
+        <v>4</v>
+      </c>
+      <c r="C142" t="n">
+        <v>4.06385953609146</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143" t="s">
+        <v>4</v>
+      </c>
+      <c r="C143" t="n">
         <v>0.9091030094148</v>
       </c>
     </row>
